--- a/data/trans_dic/P12_2_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,97</t>
+          <t>6,24; 11,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,51</t>
+          <t>5,73; 10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,72</t>
+          <t>4,62; 9,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,45; 9,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 19,05</t>
+          <t>12,19; 18,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,89</t>
+          <t>7,82; 14,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,73</t>
+          <t>7,6; 13,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,61; 21,82</t>
+          <t>10,49; 21,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 13,88</t>
+          <t>9,98; 14,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,18</t>
+          <t>7,36; 11,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,62</t>
+          <t>6,56; 10,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,33; 13,07</t>
+          <t>6,21; 12,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,76; 14,75</t>
+          <t>9,78; 14,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,9</t>
+          <t>7,29; 11,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,7</t>
+          <t>6,71; 11,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 13,72</t>
+          <t>6,35; 13,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,45; 22,0</t>
+          <t>15,72; 21,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,73</t>
+          <t>12,26; 17,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,62</t>
+          <t>8,53; 13,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 14,46</t>
+          <t>6,91; 14,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,12; 17,03</t>
+          <t>13,05; 16,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 13,89</t>
+          <t>10,15; 13,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,65</t>
+          <t>8,05; 11,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,85</t>
+          <t>7,81; 12,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,95; 19,79</t>
+          <t>14,16; 20,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,33</t>
+          <t>11,67; 17,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,99</t>
+          <t>7,54; 12,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 17,48</t>
+          <t>11,45; 17,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 25,28</t>
+          <t>18,8; 25,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 22,98</t>
+          <t>16,84; 22,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,2</t>
+          <t>11,43; 16,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 17,39</t>
+          <t>12,35; 17,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 21,77</t>
+          <t>17,63; 21,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 19,3</t>
+          <t>15,18; 19,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 13,75</t>
+          <t>10,13; 13,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 16,48</t>
+          <t>12,59; 16,46</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,6; 21,54</t>
+          <t>14,52; 21,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 19,69</t>
+          <t>13,46; 19,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,48</t>
+          <t>12,58; 18,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 17,63</t>
+          <t>4,83; 17,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 32,57</t>
+          <t>24,76; 32,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,03; 30,5</t>
+          <t>23,12; 30,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 22,78</t>
+          <t>16,84; 22,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 23,21</t>
+          <t>17,08; 23,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 25,61</t>
+          <t>20,19; 25,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,38</t>
+          <t>19,26; 24,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 19,9</t>
+          <t>15,52; 19,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,16</t>
+          <t>9,68; 19,3</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,82; 33,57</t>
+          <t>24,61; 33,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 28,18</t>
+          <t>20,03; 28,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 23,06</t>
+          <t>15,62; 23,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,13; 24,94</t>
+          <t>18,2; 24,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,43; 40,96</t>
+          <t>31,51; 40,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,27; 37,58</t>
+          <t>28,38; 37,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 32,9</t>
+          <t>24,29; 32,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,05; 31,16</t>
+          <t>25,35; 30,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,6; 36,32</t>
+          <t>29,15; 35,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,33; 31,48</t>
+          <t>25,23; 31,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,18; 27,01</t>
+          <t>21,05; 26,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,68</t>
+          <t>22,49; 26,43</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,35; 38,77</t>
+          <t>28,04; 38,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,2; 34,25</t>
+          <t>23,01; 33,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,17; 32,55</t>
+          <t>22,31; 31,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,96; 26,67</t>
+          <t>19,82; 26,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,0; 58,08</t>
+          <t>48,57; 58,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,02; 42,47</t>
+          <t>32,06; 42,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,09; 41,06</t>
+          <t>31,46; 41,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,13; 32,66</t>
+          <t>8,35; 32,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,32; 47,75</t>
+          <t>40,29; 47,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,07; 37,02</t>
+          <t>29,13; 36,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,12; 34,89</t>
+          <t>28,09; 35,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,85; 28,26</t>
+          <t>11,57; 28,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,57; 53,66</t>
+          <t>40,4; 54,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,58; 49,17</t>
+          <t>35,62; 48,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,91; 47,11</t>
+          <t>36,12; 47,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,96; 40,4</t>
+          <t>31,68; 41,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,38; 63,15</t>
+          <t>51,34; 62,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,4; 53,88</t>
+          <t>43,51; 54,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 53,08</t>
+          <t>41,51; 52,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 45,37</t>
+          <t>38,93; 45,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,78; 57,87</t>
+          <t>49,09; 58,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41,32; 49,81</t>
+          <t>41,57; 49,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,38; 49,2</t>
+          <t>40,61; 48,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,22; 42,56</t>
+          <t>37,18; 42,52</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,28; 21,04</t>
+          <t>18,2; 21,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,01; 18,69</t>
+          <t>15,92; 18,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 17,0</t>
+          <t>14,5; 16,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,14; 17,46</t>
+          <t>12,16; 17,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,97; 31,19</t>
+          <t>28,09; 31,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,99; 26,97</t>
+          <t>24,05; 27,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,83</t>
+          <t>20,88; 23,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,3; 23,51</t>
+          <t>17,9; 23,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,52; 25,71</t>
+          <t>23,6; 25,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,45; 22,52</t>
+          <t>20,49; 22,5</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,06; 20,08</t>
+          <t>18,1; 19,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,43; 20,26</t>
+          <t>16,5; 20,24</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que refirió mucha energía alguna vez o algunas veces</t>
+          <t>Población que refirió mucha energía alguna vez o algunas veces (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30942; 54187</t>
+          <t>30844; 55044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25689; 47737</t>
+          <t>26030; 48650</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19384; 40789</t>
+          <t>19379; 41119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6095; 35224</t>
+          <t>5793; 36173</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58811; 89072</t>
+          <t>56999; 87602</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32010; 59490</t>
+          <t>33482; 60125</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30544; 54321</t>
+          <t>30089; 54457</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33065; 67999</t>
+          <t>32692; 66697</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96282; 133506</t>
+          <t>95934; 136230</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62713; 98672</t>
+          <t>64962; 99692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54032; 86564</t>
+          <t>53508; 89124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45037; 92982</t>
+          <t>44174; 90919</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71770; 108504</t>
+          <t>71936; 107215</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50282; 81628</t>
+          <t>50030; 82293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38665; 69059</t>
+          <t>39598; 67478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25827; 58121</t>
+          <t>26884; 56490</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96619; 137617</t>
+          <t>98358; 135032</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72143; 108017</t>
+          <t>74672; 109275</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47480; 76623</t>
+          <t>47987; 77129</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35449; 73950</t>
+          <t>35368; 74103</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178601; 231842</t>
+          <t>177608; 231006</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131909; 179977</t>
+          <t>131533; 180924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94161; 134326</t>
+          <t>92877; 134855</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68509; 120177</t>
+          <t>73054; 120630</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89124; 126419</t>
+          <t>90419; 128755</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80704; 118191</t>
+          <t>79594; 118515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50894; 80139</t>
+          <t>50404; 81517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59989; 93594</t>
+          <t>61280; 94151</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>129810; 174342</t>
+          <t>129670; 174459</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>118945; 162930</t>
+          <t>119410; 160968</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77664; 113453</t>
+          <t>75379; 111803</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67625; 94360</t>
+          <t>67004; 93514</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>230592; 289210</t>
+          <t>234263; 291127</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208964; 268464</t>
+          <t>211128; 267955</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135978; 182594</t>
+          <t>134481; 181886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>133723; 177651</t>
+          <t>135676; 177390</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75793; 111813</t>
+          <t>75394; 110761</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81804; 120792</t>
+          <t>82583; 122609</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82097; 119152</t>
+          <t>81116; 118728</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45532; 156477</t>
+          <t>42903; 155339</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126124; 167946</t>
+          <t>127653; 167602</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>141456; 187330</t>
+          <t>142004; 187719</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>110059; 147866</t>
+          <t>109286; 148027</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120671; 165474</t>
+          <t>121755; 164935</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>211114; 265011</t>
+          <t>208937; 264111</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>234206; 299304</t>
+          <t>236434; 296205</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>201386; 257455</t>
+          <t>200878; 257003</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>145499; 306625</t>
+          <t>155006; 309007</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95967; 129826</t>
+          <t>95171; 129863</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>83586; 121018</t>
+          <t>85998; 123610</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73593; 109994</t>
+          <t>74477; 110049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101746; 139952</t>
+          <t>102130; 137423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>126971; 165460</t>
+          <t>127316; 165510</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>126587; 168305</t>
+          <t>127077; 167015</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>120206; 162706</t>
+          <t>120147; 161978</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>137115; 170548</t>
+          <t>138767; 168935</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>234068; 287206</t>
+          <t>230495; 282903</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>222208; 276142</t>
+          <t>221296; 278287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205769; 262412</t>
+          <t>204455; 259945</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>248816; 295724</t>
+          <t>249310; 293006</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82944; 113449</t>
+          <t>82051; 113570</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71876; 106105</t>
+          <t>71295; 103532</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73918; 108515</t>
+          <t>74373; 106638</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73486; 98195</t>
+          <t>72974; 98429</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>164592; 199167</t>
+          <t>166574; 200149</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>113340; 150356</t>
+          <t>113499; 150952</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>117446; 155124</t>
+          <t>118828; 155952</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>55507; 198485</t>
+          <t>50740; 198359</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256251; 303467</t>
+          <t>256059; 303880</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>192983; 245740</t>
+          <t>193366; 242853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>199977; 248077</t>
+          <t>199714; 248860</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>115654; 275853</t>
+          <t>112878; 276380</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85158; 112633</t>
+          <t>84789; 114071</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88560; 122380</t>
+          <t>88662; 121573</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92282; 121074</t>
+          <t>92819; 120880</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>90364; 114248</t>
+          <t>89590; 117064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>171560; 210848</t>
+          <t>171421; 210106</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>168802; 209577</t>
+          <t>169253; 210305</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165581; 211752</t>
+          <t>165600; 209637</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164244; 192802</t>
+          <t>165444; 194427</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>265245; 314690</t>
+          <t>266926; 315459</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>263579; 317718</t>
+          <t>265172; 318080</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>264838; 322706</t>
+          <t>266387; 319012</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>263437; 301184</t>
+          <t>263163; 300905</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1331981</t>
+          <t>1331980</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>598980; 689419</t>
+          <t>596418; 688815</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>548288; 639920</t>
+          <t>545171; 638447</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>491393; 576178</t>
+          <t>491489; 575962</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>419986; 604028</t>
+          <t>420698; 606902</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>945138; 1053966</t>
+          <t>949121; 1056738</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>852035; 957667</t>
+          <t>854156; 962705</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>738735; 843103</t>
+          <t>738815; 839917</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>632844; 859981</t>
+          <t>654772; 858035</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1565663; 1710947</t>
+          <t>1570526; 1711115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1426614; 1570610</t>
+          <t>1429118; 1569444</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1251189; 1390966</t>
+          <t>1254017; 1383754</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1169148; 1441937</t>
+          <t>1174208; 1440269</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_2_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P12_2_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,14</t>
+          <t>6,24; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,71</t>
+          <t>5,69; 11,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 9,8</t>
+          <t>4,35; 9,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 9,04</t>
+          <t>1,93; 8,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 18,74</t>
+          <t>12,52; 19,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 14,04</t>
+          <t>7,84; 14,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 13,76</t>
+          <t>7,49; 13,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 21,4</t>
+          <t>11,13; 22,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,17</t>
+          <t>9,98; 14,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,3</t>
+          <t>7,23; 11,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,93</t>
+          <t>6,8; 10,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,78</t>
+          <t>6,82; 13,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 14,58</t>
+          <t>10,0; 14,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,99</t>
+          <t>7,21; 11,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,43</t>
+          <t>6,5; 11,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 13,34</t>
+          <t>7,88; 14,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 21,59</t>
+          <t>15,4; 21,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26; 17,94</t>
+          <t>12,23; 18,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,71</t>
+          <t>8,47; 13,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,49</t>
+          <t>10,34; 16,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,97</t>
+          <t>13,22; 17,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,97</t>
+          <t>10,3; 13,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,7</t>
+          <t>7,97; 11,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,9</t>
+          <t>9,67; 14,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,16</t>
+          <t>14,39; 20,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,67; 17,38</t>
+          <t>11,79; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,2</t>
+          <t>7,35; 12,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 17,59</t>
+          <t>10,55; 16,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 25,29</t>
+          <t>18,82; 25,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,71</t>
+          <t>16,81; 22,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,95</t>
+          <t>11,78; 16,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,35; 17,24</t>
+          <t>13,16; 18,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,63; 21,92</t>
+          <t>17,43; 21,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15,18; 19,27</t>
+          <t>15,01; 19,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 13,7</t>
+          <t>10,36; 13,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 16,46</t>
+          <t>12,56; 16,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,52; 21,34</t>
+          <t>14,59; 21,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,46; 19,99</t>
+          <t>13,3; 19,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 18,41</t>
+          <t>12,47; 18,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 17,5</t>
+          <t>13,72; 19,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,76; 32,5</t>
+          <t>24,46; 32,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,12; 30,56</t>
+          <t>22,8; 30,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 22,81</t>
+          <t>16,58; 22,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 23,14</t>
+          <t>18,55; 23,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,52</t>
+          <t>20,34; 25,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 24,13</t>
+          <t>18,93; 24,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,52; 19,86</t>
+          <t>15,42; 19,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 19,3</t>
+          <t>16,98; 20,53</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,61; 33,58</t>
+          <t>24,44; 33,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,03; 28,78</t>
+          <t>19,49; 28,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,62; 23,08</t>
+          <t>15,74; 23,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,2; 24,49</t>
+          <t>17,85; 24,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,51; 40,97</t>
+          <t>31,67; 41,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,38; 37,3</t>
+          <t>28,07; 37,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 32,75</t>
+          <t>24,18; 32,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,35; 30,87</t>
+          <t>25,33; 30,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,15; 35,78</t>
+          <t>29,54; 35,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,23; 31,72</t>
+          <t>25,29; 31,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,76</t>
+          <t>21,19; 26,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,49; 26,43</t>
+          <t>22,34; 26,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,04; 38,82</t>
+          <t>27,44; 38,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,01; 33,42</t>
+          <t>23,46; 34,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,31; 31,99</t>
+          <t>22,12; 31,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,82; 26,74</t>
+          <t>18,88; 25,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,57; 58,36</t>
+          <t>47,82; 57,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,06; 42,64</t>
+          <t>32,04; 41,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,46; 41,28</t>
+          <t>31,15; 41,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,35; 32,64</t>
+          <t>28,61; 35,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,29; 47,82</t>
+          <t>40,33; 47,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29,13; 36,59</t>
+          <t>29,01; 36,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,09; 35,0</t>
+          <t>28,45; 34,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,57; 28,32</t>
+          <t>24,82; 29,45</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,4; 54,35</t>
+          <t>40,82; 54,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,62; 48,85</t>
+          <t>35,78; 48,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,12; 47,04</t>
+          <t>36,26; 47,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,68; 41,4</t>
+          <t>31,97; 41,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,34; 62,92</t>
+          <t>51,96; 62,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,51; 54,07</t>
+          <t>43,37; 53,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 52,55</t>
+          <t>41,29; 52,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,93; 45,75</t>
+          <t>38,55; 45,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49,09; 58,01</t>
+          <t>48,78; 57,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41,57; 49,87</t>
+          <t>41,79; 50,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40,61; 48,64</t>
+          <t>40,95; 49,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,18; 42,52</t>
+          <t>37,01; 42,21</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,2; 21,02</t>
+          <t>18,06; 20,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,92; 18,65</t>
+          <t>15,99; 18,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 16,99</t>
+          <t>14,51; 16,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,55</t>
+          <t>15,64; 18,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,09; 31,27</t>
+          <t>28,22; 31,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,05; 27,11</t>
+          <t>24,02; 27,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,88; 23,74</t>
+          <t>20,79; 23,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,9; 23,45</t>
+          <t>22,21; 24,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,6; 25,71</t>
+          <t>23,63; 25,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 22,5</t>
+          <t>20,47; 22,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18,1; 19,97</t>
+          <t>18,04; 20,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,5; 20,24</t>
+          <t>19,35; 21,16</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>48129</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65051</t>
+          <t>75141</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30844; 55044</t>
+          <t>30830; 55452</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26030; 48650</t>
+          <t>25844; 50104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19379; 41119</t>
+          <t>18261; 38947</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5793; 36173</t>
+          <t>7872; 35039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56999; 87602</t>
+          <t>58532; 89493</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33482; 60125</t>
+          <t>33559; 60724</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30089; 54457</t>
+          <t>29646; 53818</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32692; 66697</t>
+          <t>40167; 81071</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95934; 136230</t>
+          <t>95975; 134688</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64962; 99692</t>
+          <t>63825; 98889</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53508; 89124</t>
+          <t>55421; 87532</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44174; 90919</t>
+          <t>52469; 100603</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>66664</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95756</t>
+          <t>117869</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71936; 107215</t>
+          <t>73533; 107043</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50030; 82293</t>
+          <t>49492; 81115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39598; 67478</t>
+          <t>38362; 68000</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26884; 56490</t>
+          <t>37584; 71493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>98358; 135032</t>
+          <t>96324; 135019</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74672; 109275</t>
+          <t>74514; 111314</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47987; 77129</t>
+          <t>47631; 76970</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35368; 74103</t>
+          <t>51813; 83877</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>177608; 231006</t>
+          <t>179951; 232815</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131533; 180924</t>
+          <t>133361; 180756</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92877; 134855</t>
+          <t>91917; 135093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73054; 120630</t>
+          <t>94616; 143458</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>81508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>96594</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>155552</t>
+          <t>178102</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90419; 128755</t>
+          <t>91874; 128614</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79594; 118515</t>
+          <t>80379; 119221</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50404; 81517</t>
+          <t>49090; 82088</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61280; 94151</t>
+          <t>65379; 100124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>129670; 174459</t>
+          <t>129801; 173415</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>119410; 160968</t>
+          <t>119200; 161954</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75379; 111803</t>
+          <t>77692; 112010</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>67004; 93514</t>
+          <t>81869; 112200</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>234263; 291127</t>
+          <t>231584; 288260</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211128; 267955</t>
+          <t>208695; 267788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134481; 181886</t>
+          <t>137542; 184074</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135676; 177390</t>
+          <t>155964; 201963</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106296</t>
+          <t>115887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>144503</t>
+          <t>153500</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>250799</t>
+          <t>269387</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75394; 110761</t>
+          <t>75732; 110156</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82583; 122609</t>
+          <t>81621; 120455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81116; 118728</t>
+          <t>80448; 119910</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42903; 155339</t>
+          <t>96140; 135044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>127653; 167602</t>
+          <t>126124; 167886</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>142004; 187719</t>
+          <t>140040; 187766</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>109286; 148027</t>
+          <t>107641; 148328</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>121755; 164935</t>
+          <t>136684; 171311</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>208937; 264111</t>
+          <t>210487; 261174</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>236434; 296205</t>
+          <t>232466; 295758</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200878; 257003</t>
+          <t>199559; 256740</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>155006; 309007</t>
+          <t>244031; 295178</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118777</t>
+          <t>127482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>170266</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>271449</t>
+          <t>297748</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>95171; 129863</t>
+          <t>94529; 128879</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85998; 123610</t>
+          <t>83695; 120921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74477; 110049</t>
+          <t>75085; 110186</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>102130; 137423</t>
+          <t>108745; 147217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>127316; 165510</t>
+          <t>127950; 167681</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>127077; 167015</t>
+          <t>125694; 166882</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>120147; 161978</t>
+          <t>119607; 160922</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>138767; 168935</t>
+          <t>154074; 188173</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>230495; 282903</t>
+          <t>233547; 283702</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>221296; 278287</t>
+          <t>221885; 278067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204455; 259945</t>
+          <t>205882; 261059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>249310; 293006</t>
+          <t>271991; 325112</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>90333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>138837</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>212951</t>
+          <t>229169</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>82051; 113570</t>
+          <t>80287; 112239</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>71295; 103532</t>
+          <t>72681; 105523</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74373; 106638</t>
+          <t>73720; 105297</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72974; 98429</t>
+          <t>76865; 104506</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>166574; 200149</t>
+          <t>163983; 197969</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>113499; 150952</t>
+          <t>113407; 147268</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>118828; 155952</t>
+          <t>117689; 154895</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50740; 198359</t>
+          <t>125491; 153834</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256059; 303880</t>
+          <t>256296; 302123</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>193366; 242853</t>
+          <t>192586; 243168</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>199714; 248860</t>
+          <t>202329; 248376</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>112878; 276380</t>
+          <t>209888; 249031</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>112178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>178299</t>
+          <t>193511</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>280423</t>
+          <t>305688</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84789; 114071</t>
+          <t>85681; 113991</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>88662; 121573</t>
+          <t>89040; 121016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>92819; 120880</t>
+          <t>93190; 122268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89590; 117064</t>
+          <t>99163; 128209</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>171421; 210106</t>
+          <t>173503; 209983</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>169253; 210305</t>
+          <t>168697; 208508</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>165600; 209637</t>
+          <t>164704; 210995</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>165444; 194427</t>
+          <t>178772; 209173</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>266926; 315459</t>
+          <t>265286; 313563</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>265172; 318080</t>
+          <t>266574; 320381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>266387; 319012</t>
+          <t>268563; 321778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>263163; 300905</t>
+          <t>286428; 326625</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>544990</t>
+          <t>596210</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>786991</t>
+          <t>876895</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1331980</t>
+          <t>1473105</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>596418; 688815</t>
+          <t>591793; 681939</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>545171; 638447</t>
+          <t>547437; 641713</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>491489; 575962</t>
+          <t>491833; 575631</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>420698; 606902</t>
+          <t>552243; 642562</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>949121; 1056738</t>
+          <t>953571; 1057287</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>854156; 962705</t>
+          <t>852908; 959982</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>738815; 839917</t>
+          <t>735629; 842539</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>654772; 858035</t>
+          <t>828645; 918372</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1570526; 1711115</t>
+          <t>1573002; 1715364</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1429118; 1569444</t>
+          <t>1427648; 1571345</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1254017; 1383754</t>
+          <t>1249836; 1390239</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1174208; 1440269</t>
+          <t>1405651; 1536612</t>
         </is>
       </c>
     </row>
